--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-immunisation.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-immunisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:33:22+00:00</t>
+    <t>2026-04-24T13:15:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-immunisation.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-immunisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:15:59+00:00</t>
+    <t>2026-04-29T08:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,11 +269,11 @@
     <t>fr-lm-immunisation.header.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-usager
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient
 </t>
   </si>
   <si>
-    <t>Patient/subject information</t>
+    <t>Patient / Usager</t>
   </si>
   <si>
     <t>fr-lm-entry.header.subject</t>
@@ -446,7 +446,7 @@
     <t>fr-lm-entry.header.source</t>
   </si>
   <si>
-    <t>fr-lm-immunisation.header.langue</t>
+    <t>fr-lm-immunisation.header.language</t>
   </si>
   <si>
     <t>'fr-FR' pour français métropolitain (la casse des caractères doit être respectée)
@@ -454,7 +454,7 @@
 La partie en majuscules indique le code pays (ISO-3166)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.langue</t>
+    <t>fr-lm-entry.header.language</t>
   </si>
   <si>
     <t>fr-lm-immunisation.periodOfImmunisation</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-immunisation.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-immunisation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="201">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:17:29+00:00</t>
+    <t>2026-04-29T08:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -425,13 +425,7 @@
     <t>Statut de la vaccination (réalisé, non fait, ...).</t>
   </si>
   <si>
-    <t>Statut de l'acte</t>
-  </si>
-  <si>
-    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+    <t>Statut</t>
   </si>
   <si>
     <t>fr-lm-entry.header.status</t>
@@ -977,8 +971,8 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="47.0546875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.58203125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -2664,31 +2658,31 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>136</v>
-      </c>
       <c r="AG17" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>79</v>
@@ -2702,10 +2696,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2731,10 +2725,10 @@
         <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2785,7 +2779,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2802,10 +2796,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2831,10 +2825,10 @@
         <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2885,7 +2879,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2902,10 +2896,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2928,13 +2922,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2985,7 +2979,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -2997,15 +2991,15 @@
         <v>73</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3028,13 +3022,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="L21" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>150</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3085,7 +3079,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -3102,14 +3096,14 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3128,16 +3122,16 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3175,19 +3169,19 @@
         <v>73</v>
       </c>
       <c r="AB22" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE22" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AC22" t="s" s="2">
+      <c r="AF22" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3199,15 +3193,15 @@
         <v>73</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3230,16 +3224,16 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3289,7 +3283,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -3306,10 +3300,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3332,13 +3326,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="L24" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3389,7 +3383,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3401,15 +3395,15 @@
         <v>73</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3435,10 +3429,10 @@
         <v>127</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3489,7 +3483,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3506,10 +3500,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3535,10 +3529,10 @@
         <v>127</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3589,7 +3583,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3606,10 +3600,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3635,10 +3629,10 @@
         <v>131</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3689,7 +3683,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3706,10 +3700,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3732,13 +3726,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3789,7 +3783,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -3806,10 +3800,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3835,10 +3829,10 @@
         <v>131</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3889,7 +3883,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3906,10 +3900,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3935,10 +3929,10 @@
         <v>131</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3989,7 +3983,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -4006,10 +4000,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4032,13 +4026,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4089,7 +4083,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4106,10 +4100,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4132,13 +4126,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4189,7 +4183,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4206,10 +4200,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4232,13 +4226,13 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4289,7 +4283,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4306,10 +4300,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4332,13 +4326,13 @@
         <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4389,7 +4383,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -4406,10 +4400,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4432,13 +4426,13 @@
         <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4489,7 +4483,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -4506,10 +4500,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4535,10 +4529,10 @@
         <v>131</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4589,7 +4583,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-immunisation.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-immunisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:41:15+00:00</t>
+    <t>2026-04-30T08:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
